--- a/docs/resource-fee-template-apis.xlsx
+++ b/docs/resource-fee-template-apis.xlsx
@@ -300,69 +300,101 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="17.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="52.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22.5" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22.5" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="17.5" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="21.25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="52.5" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22.5" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22.5" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="27.5" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="37.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>TIN</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>Date_Investment_License</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>Type_of_natural_resource</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>Resource_fee_rate</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>Resource_fee_collected</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>Year_data</x:v>
-      </x:c>
-      <x:c r="G1" s="6" t="str">
-        <x:v>Use User Fallback?</x:v>
-      </x:c>
-      <x:c r="H1" s="6" t="str">
-        <x:v>User Benchmark Rate</x:v>
-      </x:c>
-      <x:c r="I1" s="6" t="str">
-        <x:v>User Benchmark Fee</x:v>
-      </x:c>
-      <x:c r="J1" s="6" t="str">
-        <x:v>User TE</x:v>
-      </x:c>
-      <x:c r="K1" s="6" t="str">
-        <x:v>User Fallback Reason</x:v>
-      </x:c>
-      <x:c r="L1" s="6" t="str">
-        <x:v>User Comment</x:v>
+      <x:c r="A1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>TIN</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Date_Investment_License</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Type_of_natural_resource</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Resource_fee_rate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Resource_fee_collected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Year_data</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Use User Fallback?</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>User Benchmark Rate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>User Benchmark Fee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>User TE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>User Fallback Reason</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>User Comment</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="15" t="str">
-        <x:v>123456789-000</x:v>
-      </x:c>
-      <x:c r="B2" s="16" t="str">
-        <x:v>2026-01-01</x:v>
-      </x:c>
-      <x:c r="C2" s="15" t="str">
-        <x:v>1 | Gemstones and gemstones - diamonds, rubies, sapphires, emeralds, - gemstones</x:v>
-      </x:c>
-      <x:c r="D2" s="17" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A2" s="15" t="inlineStr">
+        <x:is>
+          <x:t>123456789-000</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="16" t="inlineStr">
+        <x:is>
+          <x:t>2026-01-01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="15" t="inlineStr">
+        <x:is>
+          <x:t>1 | Gemstones and gemstones - diamonds, rubies, sapphires, emeralds, - gemstones</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" s="17" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E2" s="18" t="n">
         <x:v>50000000</x:v>
@@ -370,14 +402,16 @@
       <x:c r="F2" s="19" t="n">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="G2" s="15" t="str">
-        <x:v>No</x:v>
+      <x:c r="G2" s="15" t="inlineStr">
+        <x:is>
+          <x:t>No</x:t>
+        </x:is>
       </x:c>
       <x:c r="H2" s="17"/>
       <x:c r="I2" s="18"/>
       <x:c r="J2" s="18"/>
-      <x:c r="K2" s="15" t="str"/>
-      <x:c r="L2" s="15" t="str"/>
+      <x:c r="K2" s="15"/>
+      <x:c r="L2" s="15"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5"/>
@@ -14366,7 +14400,6 @@
       <x:c r="L1001" s="8"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:dataValidations count="5">
     <x:dataValidation type="list" allowBlank="0" showErrorMessage="1" showInputMessage="1" sqref="C2:C1001">
       <x:formula1>'Validation Lists'!$A$2:$A$15</x:formula1>
@@ -14385,6 +14418,7 @@
       <x:formula1>0</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -14399,207 +14433,299 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="str">
-        <x:v>Resource Fee Import Template - Instructions</x:v>
+      <x:c r="A1" s="24" t="inlineStr">
+        <x:is>
+          <x:t>Resource Fee Import Template - Instructions</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="27" t="str">
-        <x:v>Information Type</x:v>
-      </x:c>
-      <x:c r="B3" s="27" t="str">
-        <x:v>Color</x:v>
-      </x:c>
-      <x:c r="C3" s="27" t="str">
-        <x:v>Meaning</x:v>
-      </x:c>
-      <x:c r="D3" s="27" t="str">
-        <x:v>Examples</x:v>
+      <x:c r="A3" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Information Type</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Color</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Meaning</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Examples</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="5" t="str">
-        <x:v>Primary Required</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="str">
-        <x:v>Dark blue header, light blue input cells</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="str">
-        <x:v>Required for normal resource fee TE calculation.</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="str">
-        <x:v>TIN, natural resource type, actual rate, collected fee, year</x:v>
+      <x:c r="A4" s="5" t="inlineStr">
+        <x:is>
+          <x:t>Primary Required</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="5" t="inlineStr">
+        <x:is>
+          <x:t>Dark blue header, light blue input cells</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="5" t="inlineStr">
+        <x:is>
+          <x:t>Required for normal resource fee TE calculation.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="5" t="inlineStr">
+        <x:is>
+          <x:t>TIN, natural resource type, actual rate, collected fee, year</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="25" t="str">
-        <x:v>Primary Optional</x:v>
-      </x:c>
-      <x:c r="B5" s="25" t="str">
-        <x:v>Dark blue header, light blue cells</x:v>
-      </x:c>
-      <x:c r="C5" s="25" t="str">
-        <x:v>Useful for audit but not always required for calculation.</x:v>
-      </x:c>
-      <x:c r="D5" s="25" t="str">
-        <x:v>Date Investment License</x:v>
+      <x:c r="A5" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Primary Optional</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Dark blue header, light blue cells</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Useful for audit but not always required for calculation.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Date Investment License</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="8" t="str">
-        <x:v>User Fallback</x:v>
-      </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>Orange header, light amber input cells</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
-        <x:v>Optional user-provided benchmark or TE value used only when normal system calculation is insufficient.</x:v>
-      </x:c>
-      <x:c r="D6" s="8" t="str">
-        <x:v>User Benchmark Rate, User Benchmark Fee, User TE</x:v>
+      <x:c r="A6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>User Fallback</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Orange header, light amber input cells</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Optional user-provided benchmark or TE value used only when normal system calculation is insufficient.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>User Benchmark Rate, User Benchmark Fee, User TE</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="25" t="str">
-        <x:v>Protected Reference Sheets</x:v>
-      </x:c>
-      <x:c r="B7" s="25" t="str">
-        <x:v>Dark blue headers</x:v>
-      </x:c>
-      <x:c r="C7" s="25" t="str">
-        <x:v>Instructions, Validation Lists, and Data Dictionary are read-only.</x:v>
-      </x:c>
-      <x:c r="D7" s="25" t="str">
-        <x:v>Use Resource Fee Import for data entry.</x:v>
+      <x:c r="A7" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Protected Reference Sheets</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Dark blue headers</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Instructions, Validation Lists, and Data Dictionary are read-only.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Use Resource Fee Import for data entry.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="25" t="str"/>
-      <x:c r="B8" s="25" t="str"/>
-      <x:c r="C8" s="25" t="str"/>
-      <x:c r="D8" s="25" t="str"/>
+      <x:c r="A8" s="25"/>
+      <x:c r="B8" s="25"/>
+      <x:c r="C8" s="25"/>
+      <x:c r="D8" s="25"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="25" t="str">
-        <x:v>Rule</x:v>
-      </x:c>
-      <x:c r="B9" s="25" t="str">
-        <x:v>Description</x:v>
-      </x:c>
-      <x:c r="C9" s="25" t="str"/>
-      <x:c r="D9" s="25" t="str"/>
+      <x:c r="A9" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Rule</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Description</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="25"/>
+      <x:c r="D9" s="25"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="27" t="str">
-        <x:v>Current compatibility</x:v>
-      </x:c>
-      <x:c r="B10" s="27" t="str">
-        <x:v>Columns A:F match the current Resource Fee importer.</x:v>
-      </x:c>
-      <x:c r="C10" s="27" t="str"/>
-      <x:c r="D10" s="27" t="str"/>
+      <x:c r="A10" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Current compatibility</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Columns A:F match the current Resource Fee importer.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="27"/>
+      <x:c r="D10" s="27"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="25" t="str">
-        <x:v>Use primary first</x:v>
-      </x:c>
-      <x:c r="B11" s="25" t="str">
-        <x:v>The system uses the official resource benchmark rate and compares it with the actual resource fee rate.</x:v>
-      </x:c>
-      <x:c r="C11" s="25" t="str"/>
-      <x:c r="D11" s="25" t="str"/>
+      <x:c r="A11" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Use primary first</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="25" t="inlineStr">
+        <x:is>
+          <x:t>The system uses the official resource benchmark rate and compares it with the actual resource fee rate.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="25"/>
+      <x:c r="D11" s="25"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="25" t="str">
-        <x:v>No simple Excel calculations</x:v>
-      </x:c>
-      <x:c r="B12" s="25" t="str">
-        <x:v>Do not add Excel-calculated TE columns for simple rate math. The system should calculate benchmark fee and TE.</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="str"/>
-      <x:c r="D12" s="25" t="str"/>
+      <x:c r="A12" s="25" t="inlineStr">
+        <x:is>
+          <x:t>No simple Excel calculations</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Do not add Excel-calculated TE columns for simple rate math. The system should calculate benchmark fee and TE.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="25"/>
+      <x:c r="D12" s="25"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="25" t="str">
-        <x:v>Hybrid fallback</x:v>
-      </x:c>
-      <x:c r="B13" s="25" t="str">
-        <x:v>Use User Fallback fields only when the benchmark reference is missing, disputed, or a user-agreed value must be documented.</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="str"/>
-      <x:c r="D13" s="25" t="str"/>
+      <x:c r="A13" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Hybrid fallback</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Use User Fallback fields only when the benchmark reference is missing, disputed, or a user-agreed value must be documented.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="25"/>
+      <x:c r="D13" s="25"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="25" t="str">
-        <x:v>Dropdown field</x:v>
-      </x:c>
-      <x:c r="B14" s="25" t="str">
-        <x:v>Type_of_natural_resource uses official item number and name, for example 11 | Stone.</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="str"/>
-      <x:c r="D14" s="25" t="str"/>
+      <x:c r="A14" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Dropdown field</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Type_of_natural_resource uses official item number and name, for example 11 | Stone.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="25"/>
+      <x:c r="D14" s="25"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="25" t="str">
-        <x:v>Mandatory fields</x:v>
-      </x:c>
-      <x:c r="B15" s="25" t="str">
-        <x:v>TIN, Type_of_natural_resource, Resource_fee_rate, Resource_fee_collected, and Year_data.</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="str"/>
-      <x:c r="D15" s="25" t="str"/>
+      <x:c r="A15" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Mandatory fields</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="25" t="inlineStr">
+        <x:is>
+          <x:t>TIN, Type_of_natural_resource, Resource_fee_rate, Resource_fee_collected, and Year_data.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="25"/>
+      <x:c r="D15" s="25"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="25" t="str">
-        <x:v>Calculation note</x:v>
-      </x:c>
-      <x:c r="B16" s="25" t="str">
-        <x:v>If actual rate is below benchmark rate, the system estimates base value from collected fee and actual rate, then calculates benchmark fee.</x:v>
-      </x:c>
-      <x:c r="C16" s="25" t="str"/>
-      <x:c r="D16" s="25" t="str"/>
+      <x:c r="A16" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Calculation note</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="25" t="inlineStr">
+        <x:is>
+          <x:t>If actual rate is below benchmark rate, the system estimates base value from collected fee and actual rate, then calculates benchmark fee.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="25"/>
+      <x:c r="D16" s="25"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="25" t="str">
-        <x:v>Template version</x:v>
-      </x:c>
-      <x:c r="B17" s="25" t="str">
-        <x:v>RESOURCE_FEE_IMPORT v1.0</x:v>
-      </x:c>
-      <x:c r="C17" s="25" t="str"/>
-      <x:c r="D17" s="25" t="str"/>
+      <x:c r="A17" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Template version</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" s="25" t="inlineStr">
+        <x:is>
+          <x:t>RESOURCE_FEE_IMPORT v1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="25"/>
+      <x:c r="D17" s="25"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="25" t="str">
-        <x:v>Protection password</x:v>
-      </x:c>
-      <x:c r="B18" s="25" t="str">
-        <x:v>TaxETS2026</x:v>
-      </x:c>
-      <x:c r="C18" s="25" t="str">
-        <x:v>Used only to prevent accidental edits to read-only sheets.</x:v>
-      </x:c>
-      <x:c r="D18" s="25" t="str"/>
+      <x:c r="A18" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Protection password</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" s="25" t="inlineStr">
+        <x:is>
+          <x:t>TaxETS2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Used only to prevent accidental edits to read-only sheets.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" s="25"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="25" t="str">
-        <x:v>Import code note</x:v>
-      </x:c>
-      <x:c r="B19" s="25" t="str">
-        <x:v>The importer accepts both old plain resource codes/names and the new code | name dropdown values.</x:v>
-      </x:c>
-      <x:c r="C19" s="25" t="str"/>
-      <x:c r="D19" s="25" t="str"/>
+      <x:c r="A19" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Import code note</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" s="25" t="inlineStr">
+        <x:is>
+          <x:t>The importer accepts both old plain resource codes/names and the new code | name dropdown values.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C19" s="25"/>
+      <x:c r="D19" s="25"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="25" t="str">
-        <x:v>Agreement note</x:v>
-      </x:c>
-      <x:c r="B20" s="25" t="str">
-        <x:v>After expert agreement, fallback columns G:L can be connected to import logic if required.</x:v>
-      </x:c>
-      <x:c r="C20" s="25" t="str"/>
-      <x:c r="D20" s="25" t="str"/>
+      <x:c r="A20" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Agreement note</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B20" s="25" t="inlineStr">
+        <x:is>
+          <x:t>After expert agreement, fallback columns G:L can be connected to import logic if required.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C20" s="25"/>
+      <x:c r="D20" s="25"/>
     </x:row>
   </x:sheetData>
   <x:sheetProtection password="C3BC" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -14616,350 +14742,512 @@
   <x:cols>
     <x:col min="1" max="1" width="55" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="17.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="17.5" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="40" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="17.5" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="40" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="52.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="21" t="str">
-        <x:v>Resource Item</x:v>
-      </x:c>
-      <x:c r="B1" s="21" t="str">
-        <x:v>Item No</x:v>
-      </x:c>
-      <x:c r="C1" s="21" t="str">
-        <x:v>Resource Name</x:v>
-      </x:c>
-      <x:c r="D1" s="21" t="str">
-        <x:v>Benchmark Rate %</x:v>
-      </x:c>
-      <x:c r="E1" s="21" t="str">
-        <x:v>Start Year</x:v>
-      </x:c>
-      <x:c r="F1" s="21" t="str">
-        <x:v>End Year</x:v>
+      <x:c r="A1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Resource Item</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Item No</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Resource Name</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Benchmark Rate %</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Start Year</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>End Year</x:t>
+        </x:is>
       </x:c>
       <x:c r="G1" s="21"/>
-      <x:c r="H1" s="21" t="str">
-        <x:v>Yes/No</x:v>
-      </x:c>
-      <x:c r="I1" s="21" t="str"/>
-      <x:c r="J1" s="21" t="str">
-        <x:v>Fallback Reason</x:v>
+      <x:c r="H1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Yes/No</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I1" s="21"/>
+      <x:c r="J1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Fallback Reason</x:t>
+        </x:is>
       </x:c>
       <x:c r="K1" s="21"/>
-      <x:c r="L1" s="21" t="str">
-        <x:v>Provision Code</x:v>
-      </x:c>
-      <x:c r="M1" s="21" t="str">
-        <x:v>Provision Name</x:v>
-      </x:c>
-      <x:c r="N1" s="21" t="str">
-        <x:v>Category</x:v>
-      </x:c>
-      <x:c r="O1" s="21" t="str">
-        <x:v>Description</x:v>
+      <x:c r="L1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Provision Code</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Provision Name</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Category</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Description</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>1 | Gemstones and gemstones - diamonds, rubies, sapphires, emeralds, - gemstones</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>Gemstones and gemstones - diamonds, rubies, sapphires, emeralds, - gemstones</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t>1 | Gemstones and gemstones - diamonds, rubies, sapphires, emeralds, - gemstones</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" t="inlineStr">
+        <x:is>
+          <x:t>1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" t="inlineStr">
+        <x:is>
+          <x:t>Gemstones and gemstones - diamonds, rubies, sapphires, emeralds, - gemstones</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E2" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F2" t="str"/>
-      <x:c r="H2" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="J2" t="str"/>
-      <x:c r="L2" t="str">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="M2" t="str">
-        <x:v>6.2 Rental of State Land</x:v>
-      </x:c>
-      <x:c r="N2" t="str">
-        <x:v>Resource Fee</x:v>
-      </x:c>
-      <x:c r="O2" t="str">
-        <x:v>6.2 Rental of State Land</x:v>
+      <x:c r="F2"/>
+      <x:c r="H2" t="inlineStr">
+        <x:is>
+          <x:t>No</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J2"/>
+      <x:c r="L2" t="inlineStr">
+        <x:is>
+          <x:t>71</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M2" t="inlineStr">
+        <x:is>
+          <x:t>6.2 Rental of State Land</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N2" t="inlineStr">
+        <x:is>
+          <x:t>Resource Fee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O2" t="inlineStr">
+        <x:is>
+          <x:t>6.2 Rental of State Land</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>2 | Ornamental stone Quartz, marble, sapphire, slate, jasper</x:v>
-      </x:c>
-      <x:c r="B3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>Ornamental stone Quartz, marble, sapphire, slate, jasper</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
-        <x:v>5.00</x:v>
+      <x:c r="A3" t="inlineStr">
+        <x:is>
+          <x:t>2 | Ornamental stone Quartz, marble, sapphire, slate, jasper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" t="inlineStr">
+        <x:is>
+          <x:t>Ornamental stone Quartz, marble, sapphire, slate, jasper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" t="inlineStr">
+        <x:is>
+          <x:t>5.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E3" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F3" t="str"/>
-      <x:c r="H3" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="J3" t="str">
-        <x:v>Missing benchmark rate</x:v>
+      <x:c r="F3"/>
+      <x:c r="H3" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J3" t="inlineStr">
+        <x:is>
+          <x:t>Missing benchmark rate</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="str">
-        <x:v>2 | Semi-precious stones - agate, alexandrite - Aerolite, Hordeolite, Pyrite, Beryl, Spinel, Topaz, Kitzorite, Opal, Tourmaline, Agate, Garnet: Quartz, Amethyst</x:v>
-      </x:c>
-      <x:c r="B4" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>Semi-precious stones - agate, alexandrite - Aerolite, Hordeolite, Pyrite, Beryl, Spinel, Topaz, Kitzorite, Opal, Tourmaline, Agate, Garnet: Quartz, Amethyst</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>7.00</x:v>
+      <x:c r="A4" t="inlineStr">
+        <x:is>
+          <x:t>2 | Semi-precious stones - agate, alexandrite - Aerolite, Hordeolite, Pyrite, Beryl, Spinel, Topaz, Kitzorite, Opal, Tourmaline, Agate, Garnet: Quartz, Amethyst</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" t="inlineStr">
+        <x:is>
+          <x:t>Semi-precious stones - agate, alexandrite - Aerolite, Hordeolite, Pyrite, Beryl, Spinel, Topaz, Kitzorite, Opal, Tourmaline, Agate, Garnet: Quartz, Amethyst</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" t="inlineStr">
+        <x:is>
+          <x:t>7.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E4" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F4" t="str"/>
-      <x:c r="J4" t="str">
-        <x:v>Resource type not in reference</x:v>
+      <x:c r="F4"/>
+      <x:c r="J4" t="inlineStr">
+        <x:is>
+          <x:t>Resource type not in reference</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>3 | Coal - lignite, sub-bihumite, pyhumite, anthracite</x:v>
-      </x:c>
-      <x:c r="B5" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>Coal - lignite, sub-bihumite, pyhumite, anthracite</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>6.00</x:v>
+      <x:c r="A5" t="inlineStr">
+        <x:is>
+          <x:t>3 | Coal - lignite, sub-bihumite, pyhumite, anthracite</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" t="inlineStr">
+        <x:is>
+          <x:t>3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" t="inlineStr">
+        <x:is>
+          <x:t>Coal - lignite, sub-bihumite, pyhumite, anthracite</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" t="inlineStr">
+        <x:is>
+          <x:t>6.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E5" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F5" t="str"/>
-      <x:c r="J5" t="str">
-        <x:v>Special legal treatment</x:v>
+      <x:c r="F5"/>
+      <x:c r="J5" t="inlineStr">
+        <x:is>
+          <x:t>Special legal treatment</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>3 | Precious metals: silver, gold, platinum</x:v>
-      </x:c>
-      <x:c r="B6" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>Precious metals: silver, gold, platinum</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>7.00</x:v>
+      <x:c r="A6" t="inlineStr">
+        <x:is>
+          <x:t>3 | Precious metals: silver, gold, platinum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" t="inlineStr">
+        <x:is>
+          <x:t>3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" t="inlineStr">
+        <x:is>
+          <x:t>Precious metals: silver, gold, platinum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" t="inlineStr">
+        <x:is>
+          <x:t>7.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E6" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F6" t="str"/>
-      <x:c r="J6" t="str">
-        <x:v>Legacy assessment</x:v>
+      <x:c r="F6"/>
+      <x:c r="J6" t="inlineStr">
+        <x:is>
+          <x:t>Legacy assessment</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>4 | Base metals (non-ferrous metals) - copper, lead, tin, zinc, aluminum</x:v>
-      </x:c>
-      <x:c r="B7" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>Base metals (non-ferrous metals) - copper, lead, tin, zinc, aluminum</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>6.00</x:v>
+      <x:c r="A7" t="inlineStr">
+        <x:is>
+          <x:t>4 | Base metals (non-ferrous metals) - copper, lead, tin, zinc, aluminum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" t="inlineStr">
+        <x:is>
+          <x:t>4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" t="inlineStr">
+        <x:is>
+          <x:t>Base metals (non-ferrous metals) - copper, lead, tin, zinc, aluminum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" t="inlineStr">
+        <x:is>
+          <x:t>6.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E7" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F7" t="str"/>
-      <x:c r="J7" t="str">
-        <x:v>User judgment</x:v>
+      <x:c r="F7"/>
+      <x:c r="J7" t="inlineStr">
+        <x:is>
+          <x:t>User judgment</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>4 | Charcoal</x:v>
-      </x:c>
-      <x:c r="B8" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>Charcoal</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>2.00</x:v>
+      <x:c r="A8" t="inlineStr">
+        <x:is>
+          <x:t>4 | Charcoal</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" t="inlineStr">
+        <x:is>
+          <x:t>4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" t="inlineStr">
+        <x:is>
+          <x:t>Charcoal</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" t="inlineStr">
+        <x:is>
+          <x:t>2.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E8" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F8" t="str"/>
-      <x:c r="J8" t="str">
-        <x:v>Other</x:v>
+      <x:c r="F8"/>
+      <x:c r="J8" t="inlineStr">
+        <x:is>
+          <x:t>Other</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>5 | Steel and steel alloys: steel, titanium, manganese, chromium, vanadium, nickel, cobalt, molybdenum, stainless steel</x:v>
-      </x:c>
-      <x:c r="B9" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>Steel and steel alloys: steel, titanium, manganese, chromium, vanadium, nickel, cobalt, molybdenum, stainless steel</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>6.00</x:v>
+      <x:c r="A9" t="inlineStr">
+        <x:is>
+          <x:t>5 | Steel and steel alloys: steel, titanium, manganese, chromium, vanadium, nickel, cobalt, molybdenum, stainless steel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" t="inlineStr">
+        <x:is>
+          <x:t>5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" t="inlineStr">
+        <x:is>
+          <x:t>Steel and steel alloys: steel, titanium, manganese, chromium, vanadium, nickel, cobalt, molybdenum, stainless steel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" t="inlineStr">
+        <x:is>
+          <x:t>6.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E9" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F9" t="str"/>
-      <x:c r="J9" t="str">
-        <x:v>To be confirmed</x:v>
+      <x:c r="F9"/>
+      <x:c r="J9" t="inlineStr">
+        <x:is>
+          <x:t>To be confirmed</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>6 | Metals that have a metal oxide and interact with nonmetals Antimony, arsenic, beryllium, cadmium, bosmuth, magnesium, mercury, hydride and selenium, cosulphur, titanium, zirconium.</x:v>
-      </x:c>
-      <x:c r="B10" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>Metals that have a metal oxide and interact with nonmetals Antimony, arsenic, beryllium, cadmium, bosmuth, magnesium, mercury, hydride and selenium, cosulphur, titanium, zirconium.</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>7.00</x:v>
+      <x:c r="A10" t="inlineStr">
+        <x:is>
+          <x:t>6 | Metals that have a metal oxide and interact with nonmetals Antimony, arsenic, beryllium, cadmium, bosmuth, magnesium, mercury, hydride and selenium, cosulphur, titanium, zirconium.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" t="inlineStr">
+        <x:is>
+          <x:t>6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" t="inlineStr">
+        <x:is>
+          <x:t>Metals that have a metal oxide and interact with nonmetals Antimony, arsenic, beryllium, cadmium, bosmuth, magnesium, mercury, hydride and selenium, cosulphur, titanium, zirconium.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" t="inlineStr">
+        <x:is>
+          <x:t>7.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E10" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F10" t="str"/>
+      <x:c r="F10"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>7 | Ephedra - gypsum, anhydride, potash salt, magnesium salt</x:v>
-      </x:c>
-      <x:c r="B11" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>Ephedra - gypsum, anhydride, potash salt, magnesium salt</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>4.00</x:v>
+      <x:c r="A11" t="inlineStr">
+        <x:is>
+          <x:t>7 | Ephedra - gypsum, anhydride, potash salt, magnesium salt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" t="inlineStr">
+        <x:is>
+          <x:t>7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" t="inlineStr">
+        <x:is>
+          <x:t>Ephedra - gypsum, anhydride, potash salt, magnesium salt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" t="inlineStr">
+        <x:is>
+          <x:t>4.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E11" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F11" t="str"/>
+      <x:c r="F11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>7 | Salt to eat</x:v>
-      </x:c>
-      <x:c r="B12" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>Salt to eat</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>2.00</x:v>
+      <x:c r="A12" t="inlineStr">
+        <x:is>
+          <x:t>7 | Salt to eat</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" t="inlineStr">
+        <x:is>
+          <x:t>7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" t="inlineStr">
+        <x:is>
+          <x:t>Salt to eat</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" t="inlineStr">
+        <x:is>
+          <x:t>2.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E12" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F12" t="str"/>
+      <x:c r="F12"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>8 | Industrial minerals: fluoride, barite, phosponte, mica</x:v>
-      </x:c>
-      <x:c r="B13" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C13" t="str">
-        <x:v>Industrial minerals: fluoride, barite, phosponte, mica</x:v>
-      </x:c>
-      <x:c r="D13" t="str">
-        <x:v>4.00</x:v>
+      <x:c r="A13" t="inlineStr">
+        <x:is>
+          <x:t>8 | Industrial minerals: fluoride, barite, phosponte, mica</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" t="inlineStr">
+        <x:is>
+          <x:t>8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" t="inlineStr">
+        <x:is>
+          <x:t>Industrial minerals: fluoride, barite, phosponte, mica</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" t="inlineStr">
+        <x:is>
+          <x:t>4.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E13" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F13" t="str"/>
+      <x:c r="F13"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>9 | Land-based industrial resources - limestone, dolomite, magnesia, laterite, clay, tuff, asbestos, glass sand, tin, alunite, ore, feldspar, diorite, feldspar, hyocite, slate</x:v>
-      </x:c>
-      <x:c r="B14" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>Land-based industrial resources - limestone, dolomite, magnesia, laterite, clay, tuff, asbestos, glass sand, tin, alunite, ore, feldspar, diorite, feldspar, hyocite, slate</x:v>
-      </x:c>
-      <x:c r="D14" t="str">
-        <x:v>4.00</x:v>
+      <x:c r="A14" t="inlineStr">
+        <x:is>
+          <x:t>9 | Land-based industrial resources - limestone, dolomite, magnesia, laterite, clay, tuff, asbestos, glass sand, tin, alunite, ore, feldspar, diorite, feldspar, hyocite, slate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" t="inlineStr">
+        <x:is>
+          <x:t>9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" t="inlineStr">
+        <x:is>
+          <x:t>Land-based industrial resources - limestone, dolomite, magnesia, laterite, clay, tuff, asbestos, glass sand, tin, alunite, ore, feldspar, diorite, feldspar, hyocite, slate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" t="inlineStr">
+        <x:is>
+          <x:t>4.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E14" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F14" t="str"/>
+      <x:c r="F14"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>11 | Stone</x:v>
-      </x:c>
-      <x:c r="B15" t="str">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>Stone</x:v>
-      </x:c>
-      <x:c r="D15" t="str">
-        <x:v>3.00</x:v>
+      <x:c r="A15" t="inlineStr">
+        <x:is>
+          <x:t>11 | Stone</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" t="inlineStr">
+        <x:is>
+          <x:t>11</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" t="inlineStr">
+        <x:is>
+          <x:t>Stone</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" t="inlineStr">
+        <x:is>
+          <x:t>3.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="E15" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="F15" t="str"/>
+      <x:c r="F15"/>
     </x:row>
   </x:sheetData>
   <x:sheetProtection password="C3BC" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -14972,82 +15260,120 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="17.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="45" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="17.5" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="45" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="17.5" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="45" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="45" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="57.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="23" t="str">
-        <x:v>Item No</x:v>
-      </x:c>
-      <x:c r="B1" s="23" t="str">
-        <x:v>Natural Resource Type</x:v>
-      </x:c>
-      <x:c r="C1" s="23" t="str">
-        <x:v>Benchmark Rate %</x:v>
-      </x:c>
-      <x:c r="D1" s="23" t="str">
-        <x:v>Start Year</x:v>
-      </x:c>
-      <x:c r="E1" s="23" t="str">
-        <x:v>End Year</x:v>
+      <x:c r="A1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Item No</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Natural Resource Type</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Benchmark Rate %</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Start Year</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>End Year</x:t>
+        </x:is>
       </x:c>
       <x:c r="F1" s="23"/>
-      <x:c r="G1" s="23" t="str">
-        <x:v>Provision Code</x:v>
-      </x:c>
-      <x:c r="H1" s="23" t="str">
-        <x:v>Provision Name</x:v>
-      </x:c>
-      <x:c r="I1" s="23" t="str">
-        <x:v>Category</x:v>
-      </x:c>
-      <x:c r="J1" s="23" t="str">
-        <x:v>Description</x:v>
+      <x:c r="G1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Provision Code</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Provision Name</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Category</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Description</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>Gemstones and gemstones - diamonds, rubies, sapphires, emeralds, - gemstones</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t>1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" t="inlineStr">
+        <x:is>
+          <x:t>Gemstones and gemstones - diamonds, rubies, sapphires, emeralds, - gemstones</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="D2" t="n">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="E2"/>
-      <x:c r="G2" t="str">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H2" t="str">
-        <x:v>6.2 Rental of State Land</x:v>
-      </x:c>
-      <x:c r="I2" t="str">
-        <x:v>Resource Fee</x:v>
-      </x:c>
-      <x:c r="J2" t="str">
-        <x:v>6.2 Rental of State Land</x:v>
+      <x:c r="G2" t="inlineStr">
+        <x:is>
+          <x:t>71</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H2" t="inlineStr">
+        <x:is>
+          <x:t>6.2 Rental of State Land</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I2" t="inlineStr">
+        <x:is>
+          <x:t>Resource Fee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J2" t="inlineStr">
+        <x:is>
+          <x:t>6.2 Rental of State Land</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" t="str">
-        <x:v>Ornamental stone Quartz, marble, sapphire, slate, jasper</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>5.00</x:v>
+      <x:c r="A3" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" t="inlineStr">
+        <x:is>
+          <x:t>Ornamental stone Quartz, marble, sapphire, slate, jasper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" t="inlineStr">
+        <x:is>
+          <x:t>5.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="D3" t="n">
         <x:v>2025</x:v>
@@ -15055,14 +15381,20 @@
       <x:c r="E3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B4" t="str">
-        <x:v>Semi-precious stones - agate, alexandrite - Aerolite, Hordeolite, Pyrite, Beryl, Spinel, Topaz, Kitzorite, Opal, Tourmaline, Agate, Garnet: Quartz, Amethyst</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>7.00</x:v>
+      <x:c r="A4" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" t="inlineStr">
+        <x:is>
+          <x:t>Semi-precious stones - agate, alexandrite - Aerolite, Hordeolite, Pyrite, Beryl, Spinel, Topaz, Kitzorite, Opal, Tourmaline, Agate, Garnet: Quartz, Amethyst</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" t="inlineStr">
+        <x:is>
+          <x:t>7.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="D4" t="n">
         <x:v>2025</x:v>
@@ -15070,14 +15402,20 @@
       <x:c r="E4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B5" t="str">
-        <x:v>Coal - lignite, sub-bihumite, pyhumite, anthracite</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>6.00</x:v>
+      <x:c r="A5" t="inlineStr">
+        <x:is>
+          <x:t>3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" t="inlineStr">
+        <x:is>
+          <x:t>Coal - lignite, sub-bihumite, pyhumite, anthracite</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" t="inlineStr">
+        <x:is>
+          <x:t>6.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="D5" t="n">
         <x:v>2025</x:v>
@@ -15085,14 +15423,20 @@
       <x:c r="E5"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" t="str">
-        <x:v>Precious metals: silver, gold, platinum</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>7.00</x:v>
+      <x:c r="A6" t="inlineStr">
+        <x:is>
+          <x:t>3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" t="inlineStr">
+        <x:is>
+          <x:t>Precious metals: silver, gold, platinum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" t="inlineStr">
+        <x:is>
+          <x:t>7.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="D6" t="n">
         <x:v>2025</x:v>
@@ -15100,14 +15444,20 @@
       <x:c r="E6"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" t="str">
-        <x:v>Base metals (non-ferrous metals) - copper, lead, tin, zinc, aluminum</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>6.00</x:v>
+      <x:c r="A7" t="inlineStr">
+        <x:is>
+          <x:t>4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" t="inlineStr">
+        <x:is>
+          <x:t>Base metals (non-ferrous metals) - copper, lead, tin, zinc, aluminum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" t="inlineStr">
+        <x:is>
+          <x:t>6.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="D7" t="n">
         <x:v>2025</x:v>
@@ -15115,14 +15465,20 @@
       <x:c r="E7"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B8" t="str">
-        <x:v>Charcoal</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>2.00</x:v>
+      <x:c r="A8" t="inlineStr">
+        <x:is>
+          <x:t>4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" t="inlineStr">
+        <x:is>
+          <x:t>Charcoal</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" t="inlineStr">
+        <x:is>
+          <x:t>2.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="D8" t="n">
         <x:v>2025</x:v>
@@ -15130,14 +15486,20 @@
       <x:c r="E8"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B9" t="str">
-        <x:v>Steel and steel alloys: steel, titanium, manganese, chromium, vanadium, nickel, cobalt, molybdenum, stainless steel</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>6.00</x:v>
+      <x:c r="A9" t="inlineStr">
+        <x:is>
+          <x:t>5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" t="inlineStr">
+        <x:is>
+          <x:t>Steel and steel alloys: steel, titanium, manganese, chromium, vanadium, nickel, cobalt, molybdenum, stainless steel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" t="inlineStr">
+        <x:is>
+          <x:t>6.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="D9" t="n">
         <x:v>2025</x:v>
@@ -15145,14 +15507,20 @@
       <x:c r="E9"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B10" t="str">
-        <x:v>Metals that have a metal oxide and interact with nonmetals Antimony, arsenic, beryllium, cadmium, bosmuth, magnesium, mercury, hydride and selenium, cosulphur, titanium, zirconium.</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>7.00</x:v>
+      <x:c r="A10" t="inlineStr">
+        <x:is>
+          <x:t>6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" t="inlineStr">
+        <x:is>
+          <x:t>Metals that have a metal oxide and interact with nonmetals Antimony, arsenic, beryllium, cadmium, bosmuth, magnesium, mercury, hydride and selenium, cosulphur, titanium, zirconium.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" t="inlineStr">
+        <x:is>
+          <x:t>7.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="D10" t="n">
         <x:v>2025</x:v>
@@ -15160,14 +15528,20 @@
       <x:c r="E10"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B11" t="str">
-        <x:v>Ephedra - gypsum, anhydride, potash salt, magnesium salt</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>4.00</x:v>
+      <x:c r="A11" t="inlineStr">
+        <x:is>
+          <x:t>7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" t="inlineStr">
+        <x:is>
+          <x:t>Ephedra - gypsum, anhydride, potash salt, magnesium salt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" t="inlineStr">
+        <x:is>
+          <x:t>4.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="D11" t="n">
         <x:v>2025</x:v>
@@ -15175,14 +15549,20 @@
       <x:c r="E11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B12" t="str">
-        <x:v>Salt to eat</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>2.00</x:v>
+      <x:c r="A12" t="inlineStr">
+        <x:is>
+          <x:t>7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" t="inlineStr">
+        <x:is>
+          <x:t>Salt to eat</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" t="inlineStr">
+        <x:is>
+          <x:t>2.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="D12" t="n">
         <x:v>2025</x:v>
@@ -15190,14 +15570,20 @@
       <x:c r="E12"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B13" t="str">
-        <x:v>Industrial minerals: fluoride, barite, phosponte, mica</x:v>
-      </x:c>
-      <x:c r="C13" t="str">
-        <x:v>4.00</x:v>
+      <x:c r="A13" t="inlineStr">
+        <x:is>
+          <x:t>8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" t="inlineStr">
+        <x:is>
+          <x:t>Industrial minerals: fluoride, barite, phosponte, mica</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" t="inlineStr">
+        <x:is>
+          <x:t>4.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="D13" t="n">
         <x:v>2025</x:v>
@@ -15205,14 +15591,20 @@
       <x:c r="E13"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B14" t="str">
-        <x:v>Land-based industrial resources - limestone, dolomite, magnesia, laterite, clay, tuff, asbestos, glass sand, tin, alunite, ore, feldspar, diorite, feldspar, hyocite, slate</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>4.00</x:v>
+      <x:c r="A14" t="inlineStr">
+        <x:is>
+          <x:t>9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" t="inlineStr">
+        <x:is>
+          <x:t>Land-based industrial resources - limestone, dolomite, magnesia, laterite, clay, tuff, asbestos, glass sand, tin, alunite, ore, feldspar, diorite, feldspar, hyocite, slate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" t="inlineStr">
+        <x:is>
+          <x:t>4.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="D14" t="n">
         <x:v>2025</x:v>
@@ -15220,14 +15612,20 @@
       <x:c r="E14"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B15" t="str">
-        <x:v>Stone</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>3.00</x:v>
+      <x:c r="A15" t="inlineStr">
+        <x:is>
+          <x:t>11</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" t="inlineStr">
+        <x:is>
+          <x:t>Stone</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" t="inlineStr">
+        <x:is>
+          <x:t>3.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="D15" t="n">
         <x:v>2025</x:v>
@@ -15251,31 +15649,47 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="28" t="str">
-        <x:v>Version</x:v>
-      </x:c>
-      <x:c r="B1" s="28" t="str">
-        <x:v>Date</x:v>
-      </x:c>
-      <x:c r="C1" s="28" t="str">
-        <x:v>Owner</x:v>
-      </x:c>
-      <x:c r="D1" s="28" t="str">
-        <x:v>Change</x:v>
+      <x:c r="A1" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Version</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Date</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Owner</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Change</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="25" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="B2" s="25" t="str">
-        <x:v>2026-06-05</x:v>
-      </x:c>
-      <x:c r="C2" s="25" t="str">
-        <x:v>APIS / Tax-ETS</x:v>
-      </x:c>
-      <x:c r="D2" s="25" t="str">
-        <x:v>Initial recommended Resource Fee template with compatible A:F and user fallback G:L.</x:v>
+      <x:c r="A2" s="25" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="25" t="inlineStr">
+        <x:is>
+          <x:t>2026-06-05</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="25" t="inlineStr">
+        <x:is>
+          <x:t>APIS / Tax-ETS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Initial recommended Resource Fee template with compatible A:F and user fallback G:L.</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
